--- a/resources/templates/standard/L1100-04.xlsx
+++ b/resources/templates/standard/L1100-04.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 ＴＲＹ-ＯＵＴ 결과 보고서</t>
   </si>
@@ -772,11 +775,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -841,7 +846,7 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
@@ -855,7 +860,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -865,7 +870,7 @@
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
@@ -880,7 +885,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -894,7 +899,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -904,7 +909,7 @@
       <c r="S4" s="13"/>
       <c r="T4" s="13"/>
       <c r="U4" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4" s="14"/>
       <c r="W4" s="14"/>
@@ -919,10 +924,10 @@
     </row>
     <row r="5" ht="29.25" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -935,7 +940,7 @@
       <c r="K5" s="16"/>
       <c r="L5" s="17"/>
       <c r="M5" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
@@ -948,12 +953,12 @@
       <c r="V5" s="16"/>
       <c r="W5" s="17"/>
       <c r="X5" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="16"/>
       <c r="Z5" s="17"/>
       <c r="AA5" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB5" s="16"/>
       <c r="AC5" s="16"/>
